--- a/results/monthly_investor_report_2026-07-09.xlsx
+++ b/results/monthly_investor_report_2026-07-09.xlsx
@@ -637,7 +637,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-11 04:51</t>
+          <t>Son Güncelleme: 2026-07-12 05:12</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1134,25 +1134,25 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.0737479211520321</v>
+        <v>0.07374792115203216</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>7374.79211520321</v>
+        <v>7374.792115203216</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.0233118283326481</v>
+        <v>0.0233118283326483</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>171.919887778584</v>
+        <v>171.9198877785856</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>133.1328751118772</v>
+        <v>133.1328751118773</v>
       </c>
       <c r="I24" s="8" t="n">
         <v>122.850931549045</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.4183801650227493</v>
+        <v>0.4183801650227533</v>
       </c>
       <c r="K24" s="11" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-11 04:51</t>
+          <t>Son Güncelleme: 2026-07-12 05:12</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1790,13 +1790,13 @@
         <v>185.1000061035156</v>
       </c>
       <c r="E14" s="23" t="n">
-        <v>-0.0245806465802865</v>
+        <v>-0.0245806465802866</v>
       </c>
       <c r="F14" s="23" t="n">
         <v>0.0143885670157133</v>
       </c>
       <c r="G14" s="23" t="n">
-        <v>0.0729758361499268</v>
+        <v>0.0729758361499266</v>
       </c>
       <c r="H14" s="22" t="n">
         <v>180.5501282714762</v>
@@ -1805,7 +1805,7 @@
         <v>187.763329945945</v>
       </c>
       <c r="J14" s="22" t="n">
-        <v>198.6078338202763</v>
+        <v>198.6078338202762</v>
       </c>
       <c r="K14" s="22" t="n">
         <v>175.8450057983398</v>
@@ -1850,7 +1850,7 @@
         <v>-0.0557192483811474</v>
       </c>
       <c r="F15" s="20" t="n">
-        <v>0.0233118283326481</v>
+        <v>0.0233118283326483</v>
       </c>
       <c r="G15" s="20" t="n">
         <v>0.1272216922975995</v>
@@ -1859,7 +1859,7 @@
         <v>122.850931549045</v>
       </c>
       <c r="I15" s="19" t="n">
-        <v>133.1328751118772</v>
+        <v>133.1328751118773</v>
       </c>
       <c r="J15" s="19" t="n">
         <v>146.6515490479329</v>
@@ -1907,7 +1907,7 @@
         <v>-0.1065088329994344</v>
       </c>
       <c r="F16" s="17" t="n">
-        <v>-0.0199168792367259</v>
+        <v>-0.0199168792367256</v>
       </c>
       <c r="G16" s="17" t="n">
         <v>0.1064815305875086</v>
@@ -1916,7 +1916,7 @@
         <v>32.04059379398402</v>
       </c>
       <c r="I16" s="16" t="n">
-        <v>35.14578130876627</v>
+        <v>35.14578130876628</v>
       </c>
       <c r="J16" s="16" t="n">
         <v>39.67842836221079</v>
@@ -1964,10 +1964,10 @@
         <v>-0.0388692288111882</v>
       </c>
       <c r="F17" s="23" t="n">
-        <v>0.0138761110298257</v>
+        <v>0.0138761110298255</v>
       </c>
       <c r="G17" s="23" t="n">
-        <v>0.0600558756766196</v>
+        <v>0.0600558756766194</v>
       </c>
       <c r="H17" s="22" t="n">
         <v>100.8226193642755</v>
@@ -2048,7 +2048,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-11 04:51</t>
+          <t>Son Güncelleme: 2026-07-12 05:12</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2156,7 +2156,7 @@
         </is>
       </c>
       <c r="J4" s="17" t="n">
-        <v>0.0210892198914123</v>
+        <v>0.0210892198914124</v>
       </c>
       <c r="K4" s="17" t="n">
         <v>-0.0478684433228991</v>
@@ -2228,7 +2228,7 @@
         <v>-0.0357396440926404</v>
       </c>
       <c r="F6" s="20" t="n">
-        <v>-0.0228999651161745</v>
+        <v>-0.0228999651161747</v>
       </c>
       <c r="G6" s="20" t="n">
         <v>0.1854638270743971</v>
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="J8" s="17" t="n">
-        <v>0.0232520955933264</v>
+        <v>0.0232520955933265</v>
       </c>
       <c r="K8" s="17" t="n">
         <v>-0.008302551330894799</v>
@@ -2357,7 +2357,7 @@
         <v>0.0367495343186519</v>
       </c>
       <c r="F9" s="20" t="n">
-        <v>0.3727078620629436</v>
+        <v>0.3727078620629434</v>
       </c>
       <c r="G9" s="20" t="n">
         <v>0.6425849369727854</v>
@@ -2400,10 +2400,10 @@
         <v>0.0005405735325167</v>
       </c>
       <c r="F10" s="23" t="n">
-        <v>-0.08093340758166361</v>
+        <v>-0.08093340758166399</v>
       </c>
       <c r="G10" s="23" t="n">
-        <v>0.0492942938098481</v>
+        <v>0.0492942938098479</v>
       </c>
       <c r="H10" s="23" t="n">
         <v>0.1097622211770279</v>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="J10" s="23" t="n">
-        <v>0.0202677224988554</v>
+        <v>0.0202677224988553</v>
       </c>
       <c r="K10" s="23" t="n">
         <v>0.0143885670157133</v>
@@ -2460,7 +2460,7 @@
         <v>0.0239053454337624</v>
       </c>
       <c r="K11" s="20" t="n">
-        <v>0.0233118283326481</v>
+        <v>0.0233118283326483</v>
       </c>
     </row>
     <row r="12">
@@ -2503,7 +2503,7 @@
         <v>0.0293932688107371</v>
       </c>
       <c r="K12" s="17" t="n">
-        <v>-0.0199168792367259</v>
+        <v>-0.0199168792367256</v>
       </c>
     </row>
     <row r="13">
@@ -2529,7 +2529,7 @@
         <v>0.002868098050996</v>
       </c>
       <c r="F13" s="23" t="n">
-        <v>-0.0566546366480171</v>
+        <v>-0.0566546366480172</v>
       </c>
       <c r="G13" s="23" t="n">
         <v>0.0526843945771198</v>
@@ -2546,7 +2546,7 @@
         <v>0.021978629617714</v>
       </c>
       <c r="K13" s="23" t="n">
-        <v>0.0138761110298257</v>
+        <v>0.0138761110298255</v>
       </c>
     </row>
     <row r="14">
@@ -2618,7 +2618,7 @@
         <v>-0.1005376180013021</v>
       </c>
       <c r="G15" s="25" t="n">
-        <v>-0.1894379457411047</v>
+        <v>-0.1894379457411048</v>
       </c>
       <c r="H15" s="25" t="n">
         <v>0.0238790800857664</v>
@@ -2758,10 +2758,10 @@
         </is>
       </c>
       <c r="J18" s="25" t="n">
-        <v>0.0235486104790141</v>
+        <v>0.0235486104790142</v>
       </c>
       <c r="K18" s="25" t="n">
-        <v>0.0296295530137169</v>
+        <v>0.0296295530137167</v>
       </c>
     </row>
     <row r="19">
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="J19" s="25" t="n">
-        <v>0.0170044822584004</v>
+        <v>0.0170044822584005</v>
       </c>
       <c r="K19" s="25" t="n">
         <v>0.0999999076690971</v>
@@ -2830,7 +2830,7 @@
         <v>-0.0754716832983692</v>
       </c>
       <c r="F20" s="25" t="n">
-        <v>-0.2057957165972301</v>
+        <v>-0.20579571659723</v>
       </c>
       <c r="G20" s="25" t="n">
         <v>-0.1475556752513833</v>
@@ -2878,7 +2878,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-11 04:51</t>
+          <t>Son Güncelleme: 2026-07-12 05:12</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2997,7 +2997,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-11 04:51</t>
+          <t>Son Güncelleme: 2026-07-12 05:12</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3248,7 +3248,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-11 04:51</t>
+          <t>Son Güncelleme: 2026-07-12 05:12</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3373,7 +3373,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-11 04:51</t>
+          <t>Son Güncelleme: 2026-07-12 05:12</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3450,7 +3450,7 @@
         <v>-65.32012378828949</v>
       </c>
       <c r="G4" s="26" t="n">
-        <v>4138744.760793019</v>
+        <v>4172120.154143265</v>
       </c>
       <c r="H4" s="27" t="n">
         <v>0.0292907465429801</v>
@@ -3480,7 +3480,7 @@
         <v>568.6440061870599</v>
       </c>
       <c r="G5" s="26" t="n">
-        <v>4138744.760793019</v>
+        <v>4172120.154143265</v>
       </c>
       <c r="H5" s="27" t="n">
         <v>0.0292907465429801</v>
@@ -3510,7 +3510,7 @@
         <v>-2162.636557778162</v>
       </c>
       <c r="G6" s="26" t="n">
-        <v>4138744.760793019</v>
+        <v>4172120.154143265</v>
       </c>
       <c r="H6" s="27" t="n">
         <v>0.0292907465429801</v>
@@ -3540,7 +3540,7 @@
         <v>-4936.472651186981</v>
       </c>
       <c r="G7" s="26" t="n">
-        <v>4138744.760793019</v>
+        <v>4172120.154143265</v>
       </c>
       <c r="H7" s="27" t="n">
         <v>0.0292907465429801</v>
@@ -3570,7 +3570,7 @@
         <v>-1207.911652180035</v>
       </c>
       <c r="G8" s="26" t="n">
-        <v>4138744.760793019</v>
+        <v>4172120.154143265</v>
       </c>
       <c r="H8" s="27" t="n">
         <v>0.0292907465429801</v>
@@ -3600,7 +3600,7 @@
         <v>-71858.69713852904</v>
       </c>
       <c r="G9" s="26" t="n">
-        <v>4138744.760793019</v>
+        <v>4172120.154143265</v>
       </c>
       <c r="H9" s="27" t="n">
         <v>0.0292907465429801</v>
@@ -3630,7 +3630,7 @@
         <v>-44007.74369329773</v>
       </c>
       <c r="G10" s="26" t="n">
-        <v>4138744.760793019</v>
+        <v>4172120.154143265</v>
       </c>
       <c r="H10" s="27" t="n">
         <v>0.0292907465429801</v>
@@ -3660,7 +3660,7 @@
         <v>-59.77284158069051</v>
       </c>
       <c r="G11" s="26" t="n">
-        <v>4138744.760793019</v>
+        <v>4172120.154143265</v>
       </c>
       <c r="H11" s="27" t="n">
         <v>0.0292907465429801</v>

--- a/results/monthly_investor_report_2026-07-09.xlsx
+++ b/results/monthly_investor_report_2026-07-09.xlsx
@@ -637,7 +637,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-12 05:12</t>
+          <t>Son Güncelleme: 2026-07-13 05:21</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1251,7 +1251,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-12 05:12</t>
+          <t>Son Güncelleme: 2026-07-13 05:21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2048,7 +2048,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-12 05:12</t>
+          <t>Son Güncelleme: 2026-07-13 05:21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2878,7 +2878,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-12 05:12</t>
+          <t>Son Güncelleme: 2026-07-13 05:21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2997,7 +2997,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-12 05:12</t>
+          <t>Son Güncelleme: 2026-07-13 05:21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3248,7 +3248,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-12 05:12</t>
+          <t>Son Güncelleme: 2026-07-13 05:21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3373,7 +3373,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-12 05:12</t>
+          <t>Son Güncelleme: 2026-07-13 05:21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3450,7 +3450,7 @@
         <v>-65.32012378828949</v>
       </c>
       <c r="G4" s="26" t="n">
-        <v>4172120.154143265</v>
+        <v>4205495.547493511</v>
       </c>
       <c r="H4" s="27" t="n">
         <v>0.0292907465429801</v>
@@ -3480,7 +3480,7 @@
         <v>568.6440061870599</v>
       </c>
       <c r="G5" s="26" t="n">
-        <v>4172120.154143265</v>
+        <v>4205495.547493511</v>
       </c>
       <c r="H5" s="27" t="n">
         <v>0.0292907465429801</v>
@@ -3510,7 +3510,7 @@
         <v>-2162.636557778162</v>
       </c>
       <c r="G6" s="26" t="n">
-        <v>4172120.154143265</v>
+        <v>4205495.547493511</v>
       </c>
       <c r="H6" s="27" t="n">
         <v>0.0292907465429801</v>
@@ -3540,7 +3540,7 @@
         <v>-4936.472651186981</v>
       </c>
       <c r="G7" s="26" t="n">
-        <v>4172120.154143265</v>
+        <v>4205495.547493511</v>
       </c>
       <c r="H7" s="27" t="n">
         <v>0.0292907465429801</v>
@@ -3570,7 +3570,7 @@
         <v>-1207.911652180035</v>
       </c>
       <c r="G8" s="26" t="n">
-        <v>4172120.154143265</v>
+        <v>4205495.547493511</v>
       </c>
       <c r="H8" s="27" t="n">
         <v>0.0292907465429801</v>
@@ -3600,7 +3600,7 @@
         <v>-71858.69713852904</v>
       </c>
       <c r="G9" s="26" t="n">
-        <v>4172120.154143265</v>
+        <v>4205495.547493511</v>
       </c>
       <c r="H9" s="27" t="n">
         <v>0.0292907465429801</v>
@@ -3630,7 +3630,7 @@
         <v>-44007.74369329773</v>
       </c>
       <c r="G10" s="26" t="n">
-        <v>4172120.154143265</v>
+        <v>4205495.547493511</v>
       </c>
       <c r="H10" s="27" t="n">
         <v>0.0292907465429801</v>
@@ -3660,7 +3660,7 @@
         <v>-59.77284158069051</v>
       </c>
       <c r="G11" s="26" t="n">
-        <v>4172120.154143265</v>
+        <v>4205495.547493511</v>
       </c>
       <c r="H11" s="27" t="n">
         <v>0.0292907465429801</v>
